--- a/2. Gaps/coverage_matrix.xlsx
+++ b/2. Gaps/coverage_matrix.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P213"/>
+  <dimension ref="A1:P218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -482,12 +482,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Current Status</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Additional Info Added</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Current Status</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -1121,13 +1121,21 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>We don't use EC2</t>
+        </is>
+      </c>
       <c r="I10" s="2" t="inlineStr"/>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>Millie does not run general-purpose EC2 instances for application workloads (compute is on Aptible); volumes used by AWS-managed services and any incidental EC2 are encrypted, consistent with Information Security Framework §5.</t>
+          <t>We don't use EC2 Millie does not run general-purpose EC2 instances for application workloads (compute is on Aptible); volumes used by AWS-managed services and any incidental EC2 are encrypted, consistent with Information Security Framework §5.</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2834,14 +2842,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>We are going through a security assessment to open a Millie/ECH clinic</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr"/>
@@ -2912,14 +2916,10 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>The project is focused on creating a midwifery-led model at ECH Mountain View, with run-rate 40 births per months and additional GYN care. We are assessing the security of the vendor and products we have built</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr"/>
@@ -2991,11 +2991,7 @@
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr">
         <is>
@@ -3065,11 +3061,7 @@
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr">
         <is>
@@ -3139,11 +3131,7 @@
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr">
         <is>
@@ -3213,11 +3201,7 @@
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr">
         <is>
@@ -3287,11 +3271,7 @@
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr">
         <is>
@@ -3360,14 +3340,10 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>New workflows, not changed workflows</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr"/>
@@ -3439,11 +3415,7 @@
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr">
         <is>
@@ -3513,11 +3485,7 @@
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr">
         <is>
@@ -3587,11 +3555,7 @@
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr">
         <is>
@@ -3661,11 +3625,7 @@
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr">
         <is>
@@ -3735,11 +3695,7 @@
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr">
         <is>
@@ -3808,14 +3764,10 @@
           <t>Other</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>RBAC + 2FA</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr"/>
@@ -3887,11 +3839,7 @@
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr">
         <is>
@@ -3961,11 +3909,7 @@
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Complete</t>
-        </is>
-      </c>
+      <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr">
         <is>
@@ -4731,12 +4675,12 @@
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr"/>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>support@millieclinic.com, techadmins@millieclinic.com</t>
         </is>
       </c>
-      <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="2" t="inlineStr"/>
       <c r="J60" s="2" t="inlineStr">
         <is>
@@ -6407,7 +6351,11 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr"/>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G84" s="2" t="inlineStr"/>
       <c r="H84" s="2" t="inlineStr"/>
       <c r="I84" s="2" t="inlineStr"/>
@@ -6473,21 +6421,21 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr"/>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>FOLLOW UP</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>Remediated</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="2" t="inlineStr"/>
       <c r="J85" s="2" t="inlineStr">
         <is>
-          <t>Sensitive data is encrypted in transit and at rest per the Encryption Policy and Information Security Framework §5–§6 (TLS/FIPS-validated transport, Aptible-managed database encryption); user credentials are stored using a one-way salted hash (bcrypt or equivalent) per the Password Management Policy §III addition.</t>
+          <t>Yes. Sensitive data is encrypted in transit and at rest per the Encryption Policy and Information Security Framework §5–§6 (TLS/FIPS-validated transport, Aptible-managed database encryption); user credentials are stored using a one-way salted hash (bcrypt or equivalent) per the Password Management Policy §III addition.</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -6547,13 +6495,17 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr"/>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G86" s="2" t="inlineStr"/>
       <c r="H86" s="2" t="inlineStr"/>
       <c r="I86" s="2" t="inlineStr"/>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>Injection is mitigated through parameterized queries / ORM usage, server-side input validation, and least-privilege database accounts per the System Development Life Cycle (SDLC) &amp; Asset Lifecycle Policy §III(b)–(c) and Information Security Framework §4.</t>
+          <t>Yes. Injection is mitigated through parameterized queries / ORM usage, server-side input validation, and least-privilege database accounts per the System Development Life Cycle (SDLC) &amp; Asset Lifecycle Policy §III(b)–(c) and Information Security Framework §4.</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -6613,17 +6565,25 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr"/>
-      <c r="G87" s="2" t="inlineStr"/>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>FOLLOW UP</t>
+        </is>
+      </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>FOLLOW UP</t>
+          <t>We work with BreachLock for Pen Testing and automated checks, and our team takes AppSec into account for all features</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr"/>
       <c r="J87" s="2" t="inlineStr">
         <is>
-          <t>Yes. Security and privacy requirements are addressed throughout the lifecycle per the System Development Life Cycle (SDLC) &amp; Asset Lifecycle Policy §III(a)–(c) (planning, secure configuration, testing) with oversight from the Chief Security Officer.</t>
+          <t>We work with BreachLock for Pen Testing and automated checks, and our team takes AppSec into account for all features Yes. Security and privacy requirements are addressed throughout the lifecycle per the System Development Life Cycle (SDLC) &amp; Asset Lifecycle Policy §III(a)–(c) (planning, secure configuration, testing) with oversight from the Chief Security Officer.</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -6683,7 +6643,11 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr"/>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G88" s="2" t="inlineStr"/>
       <c r="H88" s="2" t="inlineStr"/>
       <c r="I88" s="2" t="inlineStr"/>
@@ -6749,21 +6713,25 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr"/>
-      <c r="G89" s="2" t="inlineStr"/>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>FOLLOW UP</t>
+        </is>
+      </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>FOLLOW UP</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+          <t>Clinic computers have a patch system/upgrade approval system in place. For web applications, we use Github to monitor all changes and monitor for problematic upgrades via a mix of PR reviews and Github security through Dependabot</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
       <c r="J89" s="2" t="inlineStr">
         <is>
-          <t>Yes. Vulnerability scanning runs against in-scope hosted services (Aptible, AWS) per Information Security Framework §6; dependency vulnerabilities are surfaced via GitHub Dependabot and triaged at least weekly with Critical/High remediated within 30 days and Medium within 90 days per the Framework §6 patch-SLA addition.</t>
+          <t>Clinic computers have a patch system/upgrade approval system in place. For web applications, we use Github to monitor all changes and monitor for problematic upgrades via a mix of PR reviews and Github security through Dependabot Yes. Vulnerability scanning runs against in-scope hosted services (Aptible, AWS) per Information Security Framework §6; dependency vulnerabilities are surfaced via GitHub Dependabot and triaged at least weekly with Critical/High remediated within 30 days and Medium within 90 days per the Framework §6 patch-SLA addition.</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -6823,18 +6791,18 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr"/>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>FOLLOW UP</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>Remediated</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr"/>
+      <c r="I90" s="2" t="inlineStr"/>
       <c r="J90" s="2" t="inlineStr">
         <is>
           <t>Yes. Passwords, keys, and tokens are protected per the Password Management Policy (strong construction, no shared use, deactivation on termination), the Encryption Policy (FIPS 140-2 key custody), and the §III session-token addition (signed short-lived tokens, rate-limited failed logins, session invalidation on logout / password change / role revocation).</t>
@@ -6897,7 +6865,11 @@
           <t>Full</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr"/>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G91" s="2" t="inlineStr"/>
       <c r="H91" s="2" t="inlineStr"/>
       <c r="I91" s="2" t="inlineStr"/>
@@ -6963,13 +6935,17 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr"/>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>FOLLOW UP</t>
-        </is>
-      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>Remediated</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr"/>
       <c r="I92" s="2" t="inlineStr"/>
       <c r="J92" s="2" t="inlineStr">
         <is>
@@ -7033,13 +7009,17 @@
           <t>Partial</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr"/>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>FOLLOW UP</t>
-        </is>
-      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>Remediated</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr"/>
       <c r="I93" s="2" t="inlineStr"/>
       <c r="J93" s="2" t="inlineStr">
         <is>
@@ -7103,13 +7083,17 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr"/>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="G94" s="2" t="inlineStr"/>
       <c r="H94" s="2" t="inlineStr"/>
       <c r="I94" s="2" t="inlineStr"/>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>N/A. Millie does not process, store, or transmit cardholder data on behalf of ECH; payments are outsourced to a third-party processor and Millie is a SAQ-A-style merchant with no card data in scope.</t>
+          <t>No. N/A. Millie does not process, store, or transmit cardholder data on behalf of ECH; payments are outsourced to a third-party processor and Millie is a SAQ-A-style merchant with no card data in scope.</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -7169,13 +7153,17 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr"/>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="G95" s="2" t="inlineStr"/>
       <c r="H95" s="2" t="inlineStr"/>
       <c r="I95" s="2" t="inlineStr"/>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>N/A. Because Millie has no cardholder data environment, a PCI DSS assessment is not applicable; payments are handled by a third-party PCI-compliant processor.</t>
+          <t>No. N/A. Because Millie has no cardholder data environment, a PCI DSS assessment is not applicable; payments are handled by a third-party PCI-compliant processor.</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -7235,13 +7223,17 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr"/>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G96" s="2" t="inlineStr"/>
       <c r="H96" s="2" t="inlineStr"/>
       <c r="I96" s="2" t="inlineStr"/>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>N/A. No PCI DSS assessment is performed because Millie does not handle cardholder data.</t>
+          <t>Yes. N/A. No PCI DSS assessment is performed because Millie does not handle cardholder data.</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -7301,13 +7293,17 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr"/>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G97" s="2" t="inlineStr"/>
       <c r="H97" s="2" t="inlineStr"/>
       <c r="I97" s="2" t="inlineStr"/>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>N/A. Millie does not store payment card data; tokenization and storage are handled by the third-party processor.</t>
+          <t>Yes. N/A. Millie does not store payment card data; tokenization and storage are handled by the third-party processor.</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -7367,13 +7363,17 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr"/>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G98" s="2" t="inlineStr"/>
       <c r="H98" s="2" t="inlineStr"/>
       <c r="I98" s="2" t="inlineStr"/>
       <c r="J98" s="2" t="inlineStr">
         <is>
-          <t>N/A. Millie does not store or access payment card data; the third-party processor controls access to cardholder data.</t>
+          <t>Yes. N/A. Millie does not store or access payment card data; the third-party processor controls access to cardholder data.</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -7433,13 +7433,17 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr"/>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G99" s="2" t="inlineStr"/>
       <c r="H99" s="2" t="inlineStr"/>
       <c r="I99" s="2" t="inlineStr"/>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>N/A. No cardholder data environment exists at Millie; access-control systems apply to Millie's clinical and operational systems per Information Security Framework §4, not to card data.</t>
+          <t>Yes. N/A. No cardholder data environment exists at Millie; access-control systems apply to Millie's clinical and operational systems per Information Security Framework §4, not to card data.</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -7499,7 +7503,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr"/>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G100" s="2" t="inlineStr"/>
       <c r="H100" s="2" t="inlineStr"/>
       <c r="I100" s="2" t="inlineStr"/>
@@ -7565,13 +7573,17 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr"/>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G101" s="2" t="inlineStr"/>
       <c r="H101" s="2" t="inlineStr"/>
       <c r="I101" s="2" t="inlineStr"/>
       <c r="J101" s="2" t="inlineStr">
         <is>
-          <t>Cardholder-data network protection is provided by the third-party PCI-compliant payment processor; Millie's own cloud network is protected per Information Security Framework §6 and AWS Network Security responses.</t>
+          <t>Yes. Cardholder-data network protection is provided by the third-party PCI-compliant payment processor; Millie's own cloud network is protected per Information Security Framework §6 and AWS Network Security responses.</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -7631,13 +7643,17 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr"/>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G102" s="2" t="inlineStr"/>
       <c r="H102" s="2" t="inlineStr"/>
       <c r="I102" s="2" t="inlineStr"/>
       <c r="J102" s="2" t="inlineStr">
         <is>
-          <t>N/A for cardholder-data accounts (none exist at Millie); Millie's general password rotation/management for its own systems is per the Password Management Policy.</t>
+          <t>Yes. N/A for cardholder-data accounts (none exist at Millie); Millie's general password rotation/management for its own systems is per the Password Management Policy.</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -7697,13 +7713,17 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr"/>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="G103" s="2" t="inlineStr"/>
       <c r="H103" s="2" t="inlineStr"/>
       <c r="I103" s="2" t="inlineStr"/>
       <c r="J103" s="2" t="inlineStr">
         <is>
-          <t>N/A for cardholder-data accounts (none exist at Millie); Millie's general password complexity requirements for its own systems are per the Password Management Policy §III(a) (length, character classes, prohibited patterns).</t>
+          <t>Yes. N/A for cardholder-data accounts (none exist at Millie); Millie's general password complexity requirements for its own systems are per the Password Management Policy §III(a) (length, character classes, prohibited patterns).</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -7768,12 +7788,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Millie’s Risk Management Policy requires risk assessments at least annually, reviews threats/vulnerabilities/likelihood/impact, and documents control recommendations. The Information Security &amp; Data Governance Framework also describes annual/as-needed risk assessments reviewed by leadership.</t>
         </is>
       </c>
-      <c r="H104" s="2" t="inlineStr"/>
       <c r="I104" s="2" t="inlineStr"/>
       <c r="J104" s="2" t="inlineStr">
         <is>
@@ -7842,12 +7862,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Yes, scoped to vendors that handle PHI or other sensitive Millie data. Millie maintains a third-party risk management process through its HIPAA Business Associate Agreement policy and Information Security &amp; Data Governance Framework. Vendors that create, receive, maintain, or transmit PHI on Millie’s behalf must execute a BAA before access is granted, accounts are created, or payment is made. Contract renewals are monitored by the Chief Privacy Officer, and executed BAAs are maintained centrally. Millie’s BAA/subcontractor terms require downstream subcontractors that create, receive, maintain, or transmit PHI to agree in writing to the same restrictions, conditions, and requirements. Millie is also maintaining vendor/platform inventories and can review critical vendors and sub-processors as part of ongoing security and compliance governance.</t>
         </is>
       </c>
-      <c r="H105" s="2" t="inlineStr"/>
       <c r="I105" s="2" t="inlineStr"/>
       <c r="J105" s="2" t="inlineStr">
         <is>
@@ -7916,12 +7936,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>BAA includes this</t>
         </is>
       </c>
-      <c r="H106" s="2" t="inlineStr"/>
       <c r="I106" s="2" t="inlineStr"/>
       <c r="J106" s="2" t="inlineStr">
         <is>
@@ -7990,12 +8010,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Millie’s Risk Management Policy requires risk assessments at least annually, reviews threats/vulnerabilities/likelihood/impact, and documents control recommendations. The Information Security &amp; Data Governance Framework also describes annual/as-needed risk assessments reviewed by leadership.</t>
         </is>
       </c>
-      <c r="H107" s="2" t="inlineStr"/>
       <c r="I107" s="2" t="inlineStr"/>
       <c r="J107" s="2" t="inlineStr">
         <is>
@@ -8064,12 +8084,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="H108" s="2" t="inlineStr"/>
       <c r="I108" s="2" t="inlineStr"/>
       <c r="J108" s="2" t="inlineStr">
         <is>
@@ -8344,9 +8364,17 @@
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr"/>
-      <c r="G112" s="2" t="inlineStr"/>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>FOLLOW UP</t>
+        </is>
+      </c>
       <c r="H112" s="2" t="inlineStr"/>
-      <c r="I112" s="2" t="inlineStr"/>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>FOLLOW UP</t>
+        </is>
+      </c>
       <c r="J112" s="2" t="inlineStr">
         <is>
           <t>N/A as a standalone security-team-owned policy. HR policies (background checks, performance reviews, sanctions) are administered through Gusto and reviewed by Millie's People Ops function; security obligations on personnel are codified in the Safeguards Policy and Workstation Use Policy.</t>
@@ -8410,9 +8438,17 @@
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr"/>
-      <c r="G113" s="2" t="inlineStr"/>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>FOLLOW UP</t>
+        </is>
+      </c>
       <c r="H113" s="2" t="inlineStr"/>
-      <c r="I113" s="2" t="inlineStr"/>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>FOLLOW UP</t>
+        </is>
+      </c>
       <c r="J113" s="2" t="inlineStr">
         <is>
           <t>N/A. Employee performance is managed through Millie's People Ops function via Gusto with periodic management review; no separate security-program-controlled performance process is maintained at Millie's headcount.</t>
@@ -9813,12 +9849,12 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr">
         <is>
           <t>FOLLOW UP</t>
         </is>
       </c>
+      <c r="H133" s="2" t="inlineStr"/>
       <c r="I133" s="2" t="inlineStr"/>
       <c r="J133" s="2" t="inlineStr">
         <is>
@@ -10307,12 +10343,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>FOLLOW UP</t>
         </is>
       </c>
+      <c r="H140" s="2" t="inlineStr"/>
       <c r="I140" s="2" t="inlineStr"/>
       <c r="J140" s="2" t="inlineStr">
         <is>
@@ -11012,12 +11048,12 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr">
         <is>
           <t>FOLLOW UP</t>
         </is>
       </c>
+      <c r="H150" s="2" t="inlineStr"/>
       <c r="I150" s="2" t="inlineStr"/>
       <c r="J150" s="2" t="inlineStr">
         <is>
@@ -11086,12 +11122,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>FOLLOW UP</t>
         </is>
       </c>
+      <c r="H151" s="2" t="inlineStr"/>
       <c r="I151" s="2" t="inlineStr"/>
       <c r="J151" s="2" t="inlineStr">
         <is>
@@ -11160,12 +11196,12 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr">
         <is>
           <t>FOLLOW UP</t>
         </is>
       </c>
+      <c r="H152" s="2" t="inlineStr"/>
       <c r="I152" s="2" t="inlineStr"/>
       <c r="J152" s="2" t="inlineStr">
         <is>
@@ -11229,7 +11265,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr"/>
+      <c r="F153" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G153" s="2" t="inlineStr"/>
       <c r="H153" s="2" t="inlineStr"/>
       <c r="I153" s="2" t="inlineStr"/>
@@ -13045,7 +13085,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr"/>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G179" s="2" t="inlineStr"/>
       <c r="H179" s="2" t="inlineStr"/>
       <c r="I179" s="2" t="inlineStr"/>
@@ -13181,7 +13225,11 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr"/>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="G181" s="2" t="inlineStr"/>
       <c r="H181" s="2" t="inlineStr"/>
       <c r="I181" s="2" t="inlineStr"/>
@@ -15206,27 +15254,28 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>Insurances</t>
+          <t>SIG Lite 2025</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>Insurances</t>
+          <t>T. Threat Management</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>T.1</t>
         </is>
       </c>
       <c r="D211" s="2" t="inlineStr">
         <is>
-          <t>Do you have document "Cyber Liability / Data Privacy"?</t>
+          <t xml:space="preserve">Is there a centrally managed Vulnerability Management Program and associated Policy that has been approved by management, communicated to appropriate constituents and an owner assigned to maintain and review the policy?
+</t>
         </is>
       </c>
       <c r="E211" s="2" t="inlineStr">
         <is>
-          <t>Evidence-only</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F211" s="2" t="inlineStr"/>
@@ -15235,64 +15284,65 @@
       <c r="I211" s="2" t="inlineStr"/>
       <c r="J211" s="2" t="inlineStr">
         <is>
-          <t>Per the HIPAA Contingency Planning Policy §III(g), the Chief Security Officer and General Counsel maintain cyber liability / data privacy insurance; the current cyber-liability certificate will be attached to the submission package.</t>
+          <t>Partial. Operationally Millie is continuously monitored via Tenisi-managed ConnectSecure with scans twice monthly (Patch Tuesday + 2-week follow-up). The `01c. Risk Management Policy` describes annual risk assessments and mitigation, and `06b. SDLC &amp; Asset Lifecycle Policy` §III(d) defines a patch-management SLA. A discretely titled Vulnerability Management Program Policy with named owner and review cadence is not yet on file — same gap as ECH OWASP A06 / SIG N.4.</t>
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr">
         <is>
-          <t>Can you provide a current cyber-liability / data-privacy insurance certificate?</t>
+          <t>Do you have a written, approved program for finding and fixing security weaknesses (with a named owner)?</t>
         </is>
       </c>
       <c r="L211" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M211" s="2" t="inlineStr">
         <is>
-          <t>Contingency Planning Policy commits to obtaining the coverage but the actual certificate is the deliverable; submission must include the certificate as an attachment.</t>
+          <t>Vulnerability scanning is operational, but a stand-alone VM Program Policy with named owner is not documented.</t>
         </is>
       </c>
       <c r="N211" s="2" t="inlineStr">
         <is>
-          <t>N/A — submission package</t>
+          <t>01c. Risk Management Policy.md</t>
         </is>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
-          <t>Attach the actual document to the ECH submission package; no policy edit.</t>
+          <t>Append 1-paragraph clause: Millie operates a Vulnerability Management Program owned by the Chief Security Officer in coordination with Tenisi. Continuous scanning is performed via ConnectSecure twice monthly (post-Patch Tuesday and 2-week follow-up). Findings are triaged per the SDLC patch SLA (Critical=7d, High=30d, Medium=90d). The program is reviewed annually alongside the security risk assessment.</t>
         </is>
       </c>
       <c r="P211" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>53</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>Security Audits</t>
+          <t>SIG Lite 2025</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>Security Audits</t>
+          <t>T. Threat Management</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>T.2</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
         <is>
-          <t>Do you have document "Penetration Testing"?</t>
+          <t xml:space="preserve">Does the organization maintain policies, standards, and procedures for identifying and managing cyber supply chain risks (i.e., ensuring software and hardware components used as part of delivering a service or product do not present a risk)?
+</t>
         </is>
       </c>
       <c r="E212" s="2" t="inlineStr">
         <is>
-          <t>Evidence-only</t>
+          <t>Partial</t>
         </is>
       </c>
       <c r="F212" s="2" t="inlineStr"/>
@@ -15301,64 +15351,65 @@
       <c r="I212" s="2" t="inlineStr"/>
       <c r="J212" s="2" t="inlineStr">
         <is>
-          <t>No third-party penetration testing report is currently on file; Millie's Chief Security Officer plans to commission a third-party penetration test and will share the report when available.</t>
+          <t>Partial. This duplicates the existing SIG S.32 / S.57 / S.61 / S.80 / S.100 gap — Millie's `01a. Information Security Framework` §11 covers third-party / vendor risk and Nth-party flow-down via BAA, but is not framed as a Cybersecurity Supply Chain Risk Management (C-SCRM) program with explicit strategy/objectives/owner. Same one-paragraph addition to Framework §11 closes both.</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
         <is>
-          <t>Can you provide a recent third-party penetration-testing report?</t>
+          <t>Do you have a written program for managing cybersecurity risk in your software/hardware supply chain?</t>
         </is>
       </c>
       <c r="L212" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="M212" s="2" t="inlineStr">
         <is>
-          <t>No pentest evidence exists; either commission a third-party pentest (recommended) or answer truthfully that none is on file. Submission impact depends on ECH appetite.</t>
+          <t>Third-party risk mgmt exists but is not framed as C-SCRM. Same fix as SIG S.32.</t>
         </is>
       </c>
       <c r="N212" s="2" t="inlineStr">
         <is>
-          <t>N/A — submission package</t>
+          <t>01a. Information Security Framework.md</t>
         </is>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>Attach the actual document to the ECH submission package; no policy edit.</t>
+          <t>(Same C-SCRM paragraph proposed for SIG S.32 — see that row. One addition closes T.2 + S.32 + S.57 + S.61 + S.80 + S.100.)</t>
         </is>
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>Security Audits</t>
+          <t>SIG Lite 2025</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>Security Audits</t>
+          <t>U. Server Security</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>U.1</t>
         </is>
       </c>
       <c r="D213" s="2" t="inlineStr">
         <is>
-          <t>Do you have document "General Security Audit"?</t>
+          <t xml:space="preserve">Are servers used for transmitting, processing, or storing scoped data?
+</t>
         </is>
       </c>
       <c r="E213" s="2" t="inlineStr">
         <is>
-          <t>Evidence-only</t>
+          <t>Full</t>
         </is>
       </c>
       <c r="F213" s="2" t="inlineStr"/>
@@ -15367,35 +15418,363 @@
       <c r="I213" s="2" t="inlineStr"/>
       <c r="J213" s="2" t="inlineStr">
         <is>
+          <t>No on-premise servers. Millie's stack is fully cloud-native (Aptible-managed application + databases on AWS, with Cloudflare DNS/CDN and Google Workspace for staff). See `01a. Information Security Framework` §5 (Data Storage &amp; Protection) and `04a. Contingency Planning Policy`. All in-scope data lives in vendor-managed cloud services.</t>
+        </is>
+      </c>
+      <c r="K213" s="2" t="inlineStr">
+        <is>
+          <t>Do you have any in-house servers that hold customer / patient data?</t>
+        </is>
+      </c>
+      <c r="L213" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N213" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O213" s="2" t="inlineStr"/>
+      <c r="P213" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="2" t="inlineStr">
+        <is>
+          <t>SIG Lite 2025</t>
+        </is>
+      </c>
+      <c r="B214" s="2" t="inlineStr">
+        <is>
+          <t>V. Cloud Services</t>
+        </is>
+      </c>
+      <c r="C214" s="2" t="inlineStr">
+        <is>
+          <t>V.1</t>
+        </is>
+      </c>
+      <c r="D214" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Are Cloud Hosting services provided?
+</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G214" s="2" t="inlineStr"/>
+      <c r="H214" s="2" t="inlineStr"/>
+      <c r="I214" s="2" t="inlineStr"/>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>No. Millie does not provide cloud-hosting services to third parties. Millie is a consumer of cloud services (Aptible, AWS, Cloudflare, Google Workspace) for its own clinical and corporate systems. See `01a. Information Security Framework` §5 and the `Supporting Sources/Millie Matrix of Platforms, Software Subscriptions, and Access` for the vendor / SaaS inventory.</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>Do *you* offer cloud-hosting services to other companies?</t>
+        </is>
+      </c>
+      <c r="L214" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N214" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O214" s="2" t="inlineStr"/>
+      <c r="P214" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="2" t="inlineStr">
+        <is>
+          <t>SIG Lite 2025</t>
+        </is>
+      </c>
+      <c r="B215" s="2" t="inlineStr">
+        <is>
+          <t>V. Cloud Services</t>
+        </is>
+      </c>
+      <c r="C215" s="2" t="inlineStr">
+        <is>
+          <t>V.2</t>
+        </is>
+      </c>
+      <c r="D215" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Does the Cloud Hosting Provider provide independent audit reports for their cloud hosting services (e.g., Service Operational Control - SOC)?
+</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F215" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="G215" s="2" t="inlineStr"/>
+      <c r="H215" s="2" t="inlineStr"/>
+      <c r="I215" s="2" t="inlineStr"/>
+      <c r="J215" s="2" t="inlineStr">
+        <is>
+          <t>N/A — Millie does not provide cloud-hosting services (see V.1). Millie's own upstream cloud providers (AWS, Aptible, Cloudflare, Google Workspace) maintain SOC 2 / ISO 27001 / HIPAA-compliant attestations that are referenced where required in the `06a. Business Associate Agreement Policy` vendor review.</t>
+        </is>
+      </c>
+      <c r="K215" s="2" t="inlineStr">
+        <is>
+          <t>Can you share independent audit reports (like SOC 2) from your cloud hosting provider?</t>
+        </is>
+      </c>
+      <c r="L215" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N215" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O215" s="2" t="inlineStr"/>
+      <c r="P215" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="2" t="inlineStr">
+        <is>
+          <t>Insurances</t>
+        </is>
+      </c>
+      <c r="B216" s="2" t="inlineStr">
+        <is>
+          <t>Insurances</t>
+        </is>
+      </c>
+      <c r="C216" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D216" s="2" t="inlineStr">
+        <is>
+          <t>Do you have document "Cyber Liability / Data Privacy"?</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="inlineStr">
+        <is>
+          <t>Evidence-only</t>
+        </is>
+      </c>
+      <c r="F216" s="2" t="inlineStr"/>
+      <c r="G216" s="2" t="inlineStr"/>
+      <c r="H216" s="2" t="inlineStr"/>
+      <c r="I216" s="2" t="inlineStr"/>
+      <c r="J216" s="2" t="inlineStr">
+        <is>
+          <t>Per the HIPAA Contingency Planning Policy §III(g), the Chief Security Officer and General Counsel maintain cyber liability / data privacy insurance; the current cyber-liability certificate will be attached to the submission package.</t>
+        </is>
+      </c>
+      <c r="K216" s="2" t="inlineStr">
+        <is>
+          <t>Can you provide a current cyber-liability / data-privacy insurance certificate?</t>
+        </is>
+      </c>
+      <c r="L216" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t>Contingency Planning Policy commits to obtaining the coverage but the actual certificate is the deliverable; submission must include the certificate as an attachment.</t>
+        </is>
+      </c>
+      <c r="N216" s="2" t="inlineStr">
+        <is>
+          <t>N/A — submission package</t>
+        </is>
+      </c>
+      <c r="O216" s="2" t="inlineStr">
+        <is>
+          <t>Attach the actual document to the ECH submission package; no policy edit.</t>
+        </is>
+      </c>
+      <c r="P216" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="2" t="inlineStr">
+        <is>
+          <t>Security Audits</t>
+        </is>
+      </c>
+      <c r="B217" s="2" t="inlineStr">
+        <is>
+          <t>Security Audits</t>
+        </is>
+      </c>
+      <c r="C217" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D217" s="2" t="inlineStr">
+        <is>
+          <t>Do you have document "Penetration Testing"?</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="inlineStr">
+        <is>
+          <t>Evidence-only</t>
+        </is>
+      </c>
+      <c r="F217" s="2" t="inlineStr"/>
+      <c r="G217" s="2" t="inlineStr"/>
+      <c r="H217" s="2" t="inlineStr"/>
+      <c r="I217" s="2" t="inlineStr"/>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>No third-party penetration testing report is currently on file; Millie's Chief Security Officer plans to commission a third-party penetration test and will share the report when available.</t>
+        </is>
+      </c>
+      <c r="K217" s="2" t="inlineStr">
+        <is>
+          <t>Can you provide a recent third-party penetration-testing report?</t>
+        </is>
+      </c>
+      <c r="L217" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t>No pentest evidence exists; either commission a third-party pentest (recommended) or answer truthfully that none is on file. Submission impact depends on ECH appetite.</t>
+        </is>
+      </c>
+      <c r="N217" s="2" t="inlineStr">
+        <is>
+          <t>N/A — submission package</t>
+        </is>
+      </c>
+      <c r="O217" s="2" t="inlineStr">
+        <is>
+          <t>Attach the actual document to the ECH submission package; no policy edit.</t>
+        </is>
+      </c>
+      <c r="P217" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="2" t="inlineStr">
+        <is>
+          <t>Security Audits</t>
+        </is>
+      </c>
+      <c r="B218" s="2" t="inlineStr">
+        <is>
+          <t>Security Audits</t>
+        </is>
+      </c>
+      <c r="C218" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D218" s="2" t="inlineStr">
+        <is>
+          <t>Do you have document "General Security Audit"?</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="inlineStr">
+        <is>
+          <t>Evidence-only</t>
+        </is>
+      </c>
+      <c r="F218" s="2" t="inlineStr"/>
+      <c r="G218" s="2" t="inlineStr"/>
+      <c r="H218" s="2" t="inlineStr"/>
+      <c r="I218" s="2" t="inlineStr"/>
+      <c r="J218" s="2" t="inlineStr">
+        <is>
           <t>No third-party general security audit (SOC 2 / HITRUST / equivalent) is currently on file; internal risk assessments per the HIPAA Risk Management Policy are conducted annually with results provided to the Risk Review Committee and, for material risks, the Board.</t>
         </is>
       </c>
-      <c r="K213" s="2" t="inlineStr">
+      <c r="K218" s="2" t="inlineStr">
         <is>
           <t>Can you provide a recent general security audit report?</t>
         </is>
       </c>
-      <c r="L213" s="2" t="inlineStr">
+      <c r="L218" s="2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="M213" s="2" t="inlineStr">
+      <c r="M218" s="2" t="inlineStr">
         <is>
           <t>No external audit attestation; provide the annual internal HIPAA risk assessment as a compensating artifact and disclose plans for a third-party audit if planned.</t>
         </is>
       </c>
-      <c r="N213" s="2" t="inlineStr">
+      <c r="N218" s="2" t="inlineStr">
         <is>
           <t>N/A — submission package</t>
         </is>
       </c>
-      <c r="O213" s="2" t="inlineStr">
+      <c r="O218" s="2" t="inlineStr">
         <is>
           <t>Attach the actual document to the ECH submission package; no policy edit.</t>
         </is>
       </c>
-      <c r="P213" s="2" t="inlineStr">
+      <c r="P218" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
